--- a/untranslated/downloads/data-excel/13.1.1.xlsx
+++ b/untranslated/downloads/data-excel/13.1.1.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="49">
   <si>
     <t>Көрсөткүчтөрдүн аталышы</t>
   </si>
@@ -177,7 +177,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -255,6 +255,19 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -287,7 +300,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -386,6 +399,15 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -669,14 +691,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S35"/>
+  <dimension ref="A1:T35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="37.140625" customWidth="1"/>
-    <col min="3" max="3" width="36" customWidth="1"/>
+    <col min="1" max="3" width="33.42578125" customWidth="1"/>
+    <col min="4" max="20" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="26" t="s">
         <v>46</v>
       </c>
@@ -687,7 +709,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
         <v>42</v>
       </c>
@@ -698,7 +720,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="8"/>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
@@ -718,8 +740,9 @@
       <c r="Q3" s="8"/>
       <c r="R3" s="8"/>
       <c r="S3" s="8"/>
-    </row>
-    <row r="4" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T3" s="8"/>
+    </row>
+    <row r="4" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
         <v>0</v>
       </c>
@@ -777,8 +800,11 @@
       <c r="S4" s="12">
         <v>2022</v>
       </c>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T4" s="12">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
@@ -825,7 +851,7 @@
         <v>18</v>
       </c>
       <c r="P5" s="13">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="Q5" s="13">
         <v>51</v>
@@ -836,8 +862,11 @@
       <c r="S5" s="13">
         <v>135</v>
       </c>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T5" s="13">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
         <v>36</v>
       </c>
@@ -884,7 +913,7 @@
         <v>14</v>
       </c>
       <c r="P6" s="20">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Q6" s="20">
         <v>29</v>
@@ -895,8 +924,11 @@
       <c r="S6" s="20">
         <v>99</v>
       </c>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T6" s="20">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
         <v>37</v>
       </c>
@@ -954,8 +986,11 @@
       <c r="S7" s="21">
         <v>36</v>
       </c>
-    </row>
-    <row r="8" spans="1:19" s="32" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="T7" s="21">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="27" t="s">
         <v>6</v>
       </c>
@@ -1013,8 +1048,11 @@
       <c r="S8" s="31">
         <v>97</v>
       </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T8" s="31" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
         <v>36</v>
       </c>
@@ -1072,8 +1110,11 @@
       <c r="S9" s="20">
         <v>80</v>
       </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T9" s="20" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
         <v>37</v>
       </c>
@@ -1131,8 +1172,11 @@
       <c r="S10" s="21">
         <v>17</v>
       </c>
-    </row>
-    <row r="11" spans="1:19" s="32" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="T10" s="21" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>9</v>
       </c>
@@ -1190,8 +1234,11 @@
       <c r="S11" s="34">
         <v>17</v>
       </c>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T11" s="34">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
         <v>36</v>
       </c>
@@ -1249,8 +1296,11 @@
       <c r="S12" s="20">
         <v>11</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T12" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
         <v>37</v>
       </c>
@@ -1300,7 +1350,7 @@
         <v>33</v>
       </c>
       <c r="Q13" s="21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R13" s="21">
         <v>7</v>
@@ -1308,8 +1358,11 @@
       <c r="S13" s="21">
         <v>6</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" s="32" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="T13" s="21">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>12</v>
       </c>
@@ -1356,7 +1409,7 @@
         <v>2</v>
       </c>
       <c r="P14" s="34">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q14" s="34" t="s">
         <v>33</v>
@@ -1367,8 +1420,11 @@
       <c r="S14" s="34">
         <v>5</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T14" s="34">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
         <v>36</v>
       </c>
@@ -1415,7 +1471,7 @@
         <v>1</v>
       </c>
       <c r="P15" s="20">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q15" s="20" t="s">
         <v>33</v>
@@ -1426,8 +1482,11 @@
       <c r="S15" s="20">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T15" s="20">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
         <v>37</v>
       </c>
@@ -1485,8 +1544,11 @@
       <c r="S16" s="21">
         <v>2</v>
       </c>
-    </row>
-    <row r="17" spans="1:19" s="32" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="T16" s="21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>15</v>
       </c>
@@ -1544,8 +1606,11 @@
       <c r="S17" s="34" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T17" s="34">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
         <v>36</v>
       </c>
@@ -1603,8 +1668,11 @@
       <c r="S18" s="20" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T18" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
         <v>37</v>
       </c>
@@ -1662,8 +1730,11 @@
       <c r="S19" s="21" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="20" spans="1:19" s="32" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="T19" s="21">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>18</v>
       </c>
@@ -1721,8 +1792,11 @@
       <c r="S20" s="34">
         <v>6</v>
       </c>
-    </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T20" s="34">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
         <v>36</v>
       </c>
@@ -1780,8 +1854,11 @@
       <c r="S21" s="20">
         <v>1</v>
       </c>
-    </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T21" s="20">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
         <v>37</v>
       </c>
@@ -1839,8 +1916,11 @@
       <c r="S22" s="21">
         <v>5</v>
       </c>
-    </row>
-    <row r="23" spans="1:19" s="32" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="T22" s="21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>21</v>
       </c>
@@ -1898,8 +1978,11 @@
       <c r="S23" s="34" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T23" s="34" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
         <v>36</v>
       </c>
@@ -1957,8 +2040,11 @@
       <c r="S24" s="20" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T24" s="20" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
         <v>37</v>
       </c>
@@ -2016,8 +2102,11 @@
       <c r="S25" s="21" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="26" spans="1:19" s="32" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="T25" s="21" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>24</v>
       </c>
@@ -2075,8 +2164,11 @@
       <c r="S26" s="34">
         <v>10</v>
       </c>
-    </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T26" s="34">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A27" s="14" t="s">
         <v>36</v>
       </c>
@@ -2134,8 +2226,11 @@
       <c r="S27" s="20">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T27" s="20">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A28" s="14" t="s">
         <v>37</v>
       </c>
@@ -2193,8 +2288,11 @@
       <c r="S28" s="21">
         <v>6</v>
       </c>
-    </row>
-    <row r="29" spans="1:19" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T28" s="21">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="27" t="s">
         <v>27</v>
       </c>
@@ -2252,8 +2350,11 @@
       <c r="S29" s="34" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T29" s="34" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A30" s="14" t="s">
         <v>36</v>
       </c>
@@ -2311,8 +2412,11 @@
       <c r="S30" s="20" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T30" s="20" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A31" s="14" t="s">
         <v>37</v>
       </c>
@@ -2370,8 +2474,11 @@
       <c r="S31" s="21" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="32" spans="1:19" s="32" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="T31" s="21" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="27" t="s">
         <v>30</v>
       </c>
@@ -2429,8 +2536,11 @@
       <c r="S32" s="31" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T32" s="31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A33" s="14" t="s">
         <v>36</v>
       </c>
@@ -2488,8 +2598,11 @@
       <c r="S33" s="20" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="34" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T33" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="15" t="s">
         <v>37</v>
       </c>
@@ -2547,15 +2660,18 @@
       <c r="S34" s="24" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A35" s="14" t="s">
+      <c r="T34" s="24" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A35" s="35" t="s">
         <v>45</v>
       </c>
-      <c r="B35" s="5" t="s">
+      <c r="B35" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="C35" s="17" t="s">
+      <c r="C35" s="37" t="s">
         <v>44</v>
       </c>
     </row>
